--- a/feature-cb-ibd-ig/ValueSet-Santeon-MetingNaamCodelijst.xlsx
+++ b/feature-cb-ibd-ig/ValueSet-Santeon-MetingNaamCodelijst.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T14:27:57+00:00</t>
+    <t>2026-10-26T15:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-cb-ibd-ig/ValueSet-Santeon-MetingNaamCodelijst.xlsx
+++ b/feature-cb-ibd-ig/ValueSet-Santeon-MetingNaamCodelijst.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T15:58:19+00:00</t>
+    <t>2026-10-29T22:11:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
